--- a/data/trans_dic/P1426-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1426-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,6</t>
+          <t>1,18; 3,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,68</t>
+          <t>0,8; 2,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,42</t>
+          <t>4,9; 7,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,38</t>
+          <t>1,1; 3,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,92</t>
+          <t>0,85; 2,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,54</t>
+          <t>4,88; 7,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,18</t>
+          <t>1,34; 2,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,37</t>
+          <t>1,02; 2,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 7,27</t>
+          <t>5,26; 7,16</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -788,37 +788,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,27</t>
+          <t>0,64; 2,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,89</t>
+          <t>0,47; 1,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,5</t>
+          <t>3,72; 5,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,66</t>
+          <t>0,97; 2,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,66</t>
+          <t>1,5; 3,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,91</t>
+          <t>3,73; 5,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,23</t>
+          <t>1,03; 2,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,32</t>
+          <t>3,98; 5,49</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,13</t>
+          <t>0,4; 2,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,27</t>
+          <t>0,71; 2,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,0</t>
+          <t>2,43; 5,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,13</t>
+          <t>0,97; 3,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,19</t>
+          <t>0,97; 3,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,43</t>
+          <t>2,99; 5,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,14</t>
+          <t>0,84; 2,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,41</t>
+          <t>1,1; 2,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,18</t>
+          <t>3,02; 4,71</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,81</t>
+          <t>0,97; 2,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,04</t>
+          <t>1,15; 2,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,7</t>
+          <t>3,19; 5,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,97</t>
+          <t>1,17; 2,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,09</t>
+          <t>1,23; 3,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,11</t>
+          <t>3,65; 5,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,44</t>
+          <t>1,28; 2,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,71</t>
+          <t>1,37; 2,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,98</t>
+          <t>3,58; 5,08</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,04</t>
+          <t>1,11; 2,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,94</t>
+          <t>1,07; 1,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,18</t>
+          <t>4,05; 5,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,35</t>
+          <t>1,41; 2,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,59</t>
+          <t>1,56; 2,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,96</t>
+          <t>4,14; 5,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,06</t>
+          <t>1,41; 2,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,09</t>
+          <t>1,45; 2,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 4,94</t>
+          <t>4,23; 5,05</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40878</t>
+          <t>42675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41676</t>
+          <t>44486</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82555</t>
+          <t>87161</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8750; 25349</t>
+          <t>8330; 26509</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4947; 18093</t>
+          <t>5383; 17795</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31654; 53488</t>
+          <t>33874; 54443</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7335; 23591</t>
+          <t>7697; 24274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6087; 19656</t>
+          <t>5722; 19524</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34814; 50881</t>
+          <t>35749; 53682</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19929; 44469</t>
+          <t>18725; 41310</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14093; 31917</t>
+          <t>13725; 32095</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>70057; 95270</t>
+          <t>74810; 101808</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48115</t>
+          <t>50457</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46066</t>
+          <t>48730</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>94181</t>
+          <t>99187</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6938; 23113</t>
+          <t>6523; 23674</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4967; 19276</t>
+          <t>4854; 19439</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22810; 65611</t>
+          <t>38973; 62421</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10043; 27356</t>
+          <t>9976; 26542</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16345; 38193</t>
+          <t>15608; 36851</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36002; 56571</t>
+          <t>39886; 60975</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21444; 45743</t>
+          <t>21017; 43723</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24370; 50423</t>
+          <t>24353; 50330</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62422; 114341</t>
+          <t>84212; 116222</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24248</t>
+          <t>28878</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28085</t>
+          <t>31873</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52333</t>
+          <t>60751</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3061; 16166</t>
+          <t>3060; 16459</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5434; 17247</t>
+          <t>5400; 17765</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15951; 35059</t>
+          <t>19420; 40157</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7602; 24292</t>
+          <t>7529; 24440</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8678; 25028</t>
+          <t>7648; 23732</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14776; 41333</t>
+          <t>24284; 43024</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12602; 32911</t>
+          <t>12955; 33049</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16526; 37236</t>
+          <t>16935; 37289</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34002; 68277</t>
+          <t>48679; 75867</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40895</t>
+          <t>42100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44573</t>
+          <t>49422</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>85468</t>
+          <t>91522</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9925; 26643</t>
+          <t>9195; 26332</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11182; 28503</t>
+          <t>10804; 27635</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30559; 52852</t>
+          <t>31610; 54189</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13128; 31240</t>
+          <t>12341; 30631</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12639; 32247</t>
+          <t>12878; 33729</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33813; 55781</t>
+          <t>40809; 62848</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25506; 48889</t>
+          <t>25658; 50942</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27842; 53621</t>
+          <t>27235; 52557</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70037; 100422</t>
+          <t>75329; 106928</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154136</t>
+          <t>164110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>160400</t>
+          <t>174510</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>314536</t>
+          <t>338620</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>38818; 69833</t>
+          <t>38013; 68462</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36588; 65709</t>
+          <t>36336; 64386</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118802; 179133</t>
+          <t>143078; 185982</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50402; 83422</t>
+          <t>50236; 83816</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>57185; 91946</t>
+          <t>55309; 91540</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>130509; 181385</t>
+          <t>154437; 193746</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98274; 144032</t>
+          <t>98281; 147293</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99982; 145331</t>
+          <t>100489; 148343</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>272030; 351359</t>
+          <t>307362; 366562</t>
         </is>
       </c>
     </row>
